--- a/data/gravel/Wilier Rave SLR ID2 2025.xlsx
+++ b/data/gravel/Wilier Rave SLR ID2 2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D31F1AD-CB91-CC40-9EDF-2AA1676BF4E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFDC5CE5-24B4-4D43-A383-60CF3D2A18E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16320" yWindow="-18920" windowWidth="25680" windowHeight="16760" xr2:uid="{ABFFBBBD-2C2A-DA41-8959-3BF392F3D8AC}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{ABFFBBBD-2C2A-DA41-8959-3BF392F3D8AC}"/>
   </bookViews>
   <sheets>
     <sheet name="Wilier Rave SLR ID2 2025" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="68">
   <si>
     <t>model</t>
   </si>
@@ -237,6 +237,9 @@
   </si>
   <si>
     <t>a10:h34</t>
+  </si>
+  <si>
+    <t>grand fondo, two stem-handlebar sizes</t>
   </si>
 </sst>
 </file>
@@ -1164,16 +1167,16 @@
   </xdr:oneCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>713740</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>241300</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>396240</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>274320</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>782320</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1203,7 +1206,7 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="11572240" y="5969000"/>
+          <a:off x="11521440" y="7226300"/>
           <a:ext cx="6990080" cy="4368800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2451,7 +2454,7 @@
   <cols>
     <col min="1" max="1" width="29.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="27.6640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="31.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.1640625" style="1" customWidth="1"/>
     <col min="4" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
@@ -3237,6 +3240,27 @@
       <c r="B27" s="1" t="s">
         <v>20</v>
       </c>
+      <c r="C27" s="1">
+        <v>88</v>
+      </c>
+      <c r="D27" s="1">
+        <v>88</v>
+      </c>
+      <c r="E27" s="1">
+        <v>88</v>
+      </c>
+      <c r="F27" s="1">
+        <v>114</v>
+      </c>
+      <c r="G27" s="1">
+        <v>114</v>
+      </c>
+      <c r="H27" s="1">
+        <v>114</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="Q27"/>
     </row>
     <row r="28" spans="1:17">

--- a/data/gravel/Wilier Rave SLR ID2 2025.xlsx
+++ b/data/gravel/Wilier Rave SLR ID2 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFDC5CE5-24B4-4D43-A383-60CF3D2A18E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{534AA428-E18E-7B41-B3F7-6103CD366F8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{ABFFBBBD-2C2A-DA41-8959-3BF392F3D8AC}"/>
+    <workbookView xWindow="1280" yWindow="560" windowWidth="26060" windowHeight="15600" xr2:uid="{ABFFBBBD-2C2A-DA41-8959-3BF392F3D8AC}"/>
   </bookViews>
   <sheets>
     <sheet name="Wilier Rave SLR ID2 2025" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="101">
   <si>
     <t>model</t>
   </si>
@@ -158,12 +158,6 @@
     <t>material</t>
   </si>
   <si>
-    <t>frame weight</t>
-  </si>
-  <si>
-    <t>UDH</t>
-  </si>
-  <si>
     <t>yes</t>
   </si>
   <si>
@@ -236,10 +230,115 @@
     <t>measure range</t>
   </si>
   <si>
-    <t>a10:h34</t>
-  </si>
-  <si>
     <t>grand fondo, two stem-handlebar sizes</t>
+  </si>
+  <si>
+    <t>udh</t>
+  </si>
+  <si>
+    <t>dropout</t>
+  </si>
+  <si>
+    <t>650B tire max</t>
+  </si>
+  <si>
+    <t>suspension corrected</t>
+  </si>
+  <si>
+    <t>rear axle</t>
+  </si>
+  <si>
+    <t>front axle</t>
+  </si>
+  <si>
+    <t>q-factor</t>
+  </si>
+  <si>
+    <t>seatpost diameter</t>
+  </si>
+  <si>
+    <t>routing shifter</t>
+  </si>
+  <si>
+    <t>routing dropper</t>
+  </si>
+  <si>
+    <t>routing dynamo</t>
+  </si>
+  <si>
+    <t>front derailleur</t>
+  </si>
+  <si>
+    <t>chainring 1</t>
+  </si>
+  <si>
+    <t>chainring 2</t>
+  </si>
+  <si>
+    <t>bottom bracket</t>
+  </si>
+  <si>
+    <t>mounts inner</t>
+  </si>
+  <si>
+    <t>mounts under</t>
+  </si>
+  <si>
+    <t>mounts top</t>
+  </si>
+  <si>
+    <t>mounts fork</t>
+  </si>
+  <si>
+    <t>mounts fender rear</t>
+  </si>
+  <si>
+    <t>mounts fender front</t>
+  </si>
+  <si>
+    <t>mounts rack</t>
+  </si>
+  <si>
+    <t>rotor max front</t>
+  </si>
+  <si>
+    <t>rotor max rear</t>
+  </si>
+  <si>
+    <t>frameset</t>
+  </si>
+  <si>
+    <t>base build</t>
+  </si>
+  <si>
+    <t>currency</t>
+  </si>
+  <si>
+    <t>frame_weight</t>
+  </si>
+  <si>
+    <t>a10:h35</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>fork suspension</t>
+  </si>
+  <si>
+    <t>stem suspension</t>
+  </si>
+  <si>
+    <t>rear suspension</t>
+  </si>
+  <si>
+    <t>internal storage</t>
+  </si>
+  <si>
+    <t>700c width max</t>
+  </si>
+  <si>
+    <t>ISO ASTM</t>
   </si>
 </sst>
 </file>
@@ -249,7 +348,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -284,6 +383,12 @@
       <color rgb="FF000000"/>
       <name val="Futura Medium"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Futura"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -305,7 +410,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -314,6 +419,13 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="15" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -337,13 +449,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>32</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>32</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>50800</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -385,13 +497,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>32</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>32</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>50800</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -433,7 +545,7 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>32</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -476,7 +588,7 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>32</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -519,7 +631,7 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>32</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -562,7 +674,7 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>32</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -605,7 +717,7 @@
     <xdr:from>
       <xdr:col>9</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>30</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -739,7 +851,7 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>32</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="317500"/>
@@ -782,7 +894,7 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>32</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="317500"/>
@@ -825,7 +937,7 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>32</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="317500"/>
@@ -868,7 +980,7 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>32</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="317500"/>
@@ -911,7 +1023,7 @@
     <xdr:from>
       <xdr:col>9</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>30</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="317500"/>
@@ -954,7 +1066,7 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>32</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -997,7 +1109,7 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>32</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -1040,7 +1152,7 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>32</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -1083,7 +1195,7 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>32</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -1126,7 +1238,7 @@
     <xdr:from>
       <xdr:col>9</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>30</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -1174,7 +1286,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>782320</xdr:colOff>
+      <xdr:colOff>553720</xdr:colOff>
       <xdr:row>45</xdr:row>
       <xdr:rowOff>165100</xdr:rowOff>
     </xdr:to>
@@ -1230,7 +1342,7 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>32</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -1273,7 +1385,7 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>32</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -1316,7 +1428,7 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>32</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -1359,7 +1471,7 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>32</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -1402,7 +1514,7 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>32</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -1445,7 +1557,7 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>32</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -1488,7 +1600,7 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>32</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -1531,7 +1643,7 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>32</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -1574,7 +1686,7 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>32</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -1617,7 +1729,7 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>32</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -1660,7 +1772,7 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>32</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -1703,7 +1815,7 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>32</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -1746,7 +1858,7 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>32</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -1789,7 +1901,7 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>32</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -1832,7 +1944,7 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>32</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -1875,7 +1987,7 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>32</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -1918,7 +2030,7 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>32</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -1961,7 +2073,7 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>32</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -2004,7 +2116,7 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>32</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -2047,7 +2159,7 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>32</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -2090,7 +2202,7 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>32</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -2449,32 +2561,36 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3856DE37-3828-6849-A98A-EC05E320BDEE}">
-  <dimension ref="A1:Y36"/>
+  <dimension ref="A1:AH37"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="29.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="27.6640625" style="1" customWidth="1"/>
     <col min="3" max="3" width="13.1640625" style="1" customWidth="1"/>
-    <col min="4" max="16384" width="10.83203125" style="1"/>
+    <col min="4" max="5" width="10.83203125" style="1"/>
+    <col min="6" max="6" width="12.6640625" style="1" customWidth="1"/>
+    <col min="7" max="13" width="10.83203125" style="1"/>
+    <col min="14" max="14" width="13.83203125" style="1" customWidth="1"/>
+    <col min="15" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25">
+    <row r="1" spans="1:34">
       <c r="A1" s="1" t="s">
         <v>38</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:34">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:34">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -2482,7 +2598,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="4" spans="1:25">
+    <row r="4" spans="1:34">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -2490,47 +2606,162 @@
         <v>45845</v>
       </c>
     </row>
-    <row r="5" spans="1:25">
+    <row r="5" spans="1:34">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
-    <row r="6" spans="1:25">
-      <c r="A6" s="1" t="s">
+    <row r="6" spans="1:34" customFormat="1" ht="55" customHeight="1">
+      <c r="A6" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>62</v>
+      <c r="B6" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="K6" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="M6" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="N6" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="O6" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="P6" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q6" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="R6" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="S6" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="T6" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="U6" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="V6" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="W6" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="X6" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="Y6" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="Z6" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="AA6" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="AB6" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="AC6" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="AD6" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="AE6" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="AF6" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="AG6" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="AH6" s="9" t="s">
+        <v>98</v>
       </c>
     </row>
-    <row r="7" spans="1:25">
+    <row r="7" spans="1:34">
       <c r="A7" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B7" s="1">
-        <v>785</v>
+      <c r="C7" s="1">
+        <v>0</v>
+      </c>
+      <c r="D7" s="1">
+        <v>53</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q7" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="R7" s="1">
+        <v>50</v>
+      </c>
+      <c r="AH7" s="1" t="s">
+        <v>94</v>
       </c>
     </row>
-    <row r="8" spans="1:25">
-      <c r="A8" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>42</v>
+    <row r="9" spans="1:34">
+      <c r="A9" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>93</v>
       </c>
     </row>
-    <row r="9" spans="1:25">
-      <c r="A9" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="10" spans="1:25">
+    <row r="10" spans="1:34">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
@@ -2538,40 +2769,40 @@
         <v>4</v>
       </c>
       <c r="C10" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E10" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="F10" s="7" t="s">
         <v>44</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>46</v>
       </c>
       <c r="G10" s="7" t="s">
         <v>37</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="J10" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="K10" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="L10" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="K10" s="7" t="s">
+      <c r="M10" s="7" t="s">
         <v>44</v>
-      </c>
-      <c r="L10" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="M10" s="7" t="s">
-        <v>46</v>
       </c>
       <c r="N10" s="7" t="s">
         <v>37</v>
       </c>
       <c r="O10" s="7" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="Q10" s="2" t="s">
         <v>28</v>
@@ -2601,19 +2832,19 @@
         <v>36</v>
       </c>
     </row>
-    <row r="11" spans="1:25">
+    <row r="11" spans="1:34">
       <c r="A11" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C11" s="7">
         <f>J11*10</f>
         <v>432</v>
       </c>
       <c r="D11" s="7">
-        <f t="shared" ref="D11:H11" si="0">K11*10</f>
+        <f t="shared" ref="D11:F11" si="0">K11*10</f>
         <v>462</v>
       </c>
       <c r="E11" s="7">
@@ -2625,11 +2856,11 @@
         <v>502</v>
       </c>
       <c r="G11" s="7">
-        <f t="shared" si="0"/>
+        <f>N11*10</f>
         <v>522</v>
       </c>
       <c r="H11" s="7">
-        <f t="shared" si="0"/>
+        <f>O11*10</f>
         <v>542</v>
       </c>
       <c r="J11" s="7">
@@ -2660,12 +2891,12 @@
       <c r="X11" s="4"/>
       <c r="Y11" s="4"/>
     </row>
-    <row r="12" spans="1:25">
+    <row r="12" spans="1:34">
       <c r="A12" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C12" s="7">
         <f t="shared" ref="C12:C16" si="1">J12*10</f>
@@ -2719,12 +2950,12 @@
       <c r="X12" s="3"/>
       <c r="Y12" s="3"/>
     </row>
-    <row r="13" spans="1:25">
+    <row r="13" spans="1:34">
       <c r="A13" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C13" s="7">
         <f t="shared" si="1"/>
@@ -2778,19 +3009,19 @@
       <c r="X13" s="3"/>
       <c r="Y13" s="3"/>
     </row>
-    <row r="14" spans="1:25">
+    <row r="14" spans="1:34">
       <c r="A14" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C14" s="7">
         <f>J14</f>
         <v>75.5</v>
       </c>
       <c r="D14" s="7">
-        <f t="shared" ref="D14:H14" si="7">K14</f>
+        <f t="shared" ref="D14:F14" si="7">K14</f>
         <v>74.7</v>
       </c>
       <c r="E14" s="7">
@@ -2802,11 +3033,11 @@
         <v>73.5</v>
       </c>
       <c r="G14" s="7">
-        <f t="shared" si="7"/>
+        <f>N14</f>
         <v>73</v>
       </c>
       <c r="H14" s="7">
-        <f t="shared" si="7"/>
+        <f>O14</f>
         <v>73</v>
       </c>
       <c r="J14" s="7">
@@ -2837,12 +3068,12 @@
       <c r="X14" s="3"/>
       <c r="Y14" s="3"/>
     </row>
-    <row r="15" spans="1:25">
+    <row r="15" spans="1:34">
       <c r="A15" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C15" s="7">
         <f t="shared" si="1"/>
@@ -2896,12 +3127,12 @@
       <c r="X15" s="3"/>
       <c r="Y15" s="3"/>
     </row>
-    <row r="16" spans="1:25">
+    <row r="16" spans="1:34">
       <c r="A16" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C16" s="7">
         <f t="shared" si="1"/>
@@ -2960,7 +3191,7 @@
         <v>10</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C17" s="7">
         <v>70</v>
@@ -3004,7 +3235,7 @@
         <v>7</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C18" s="7">
         <v>375</v>
@@ -3048,7 +3279,7 @@
         <v>8</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C19" s="7">
         <v>532</v>
@@ -3093,7 +3324,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C20" s="7">
         <v>1014</v>
@@ -3159,7 +3390,7 @@
         <v>75</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="Q21"/>
     </row>
@@ -3189,7 +3420,7 @@
         <v>50</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="Q22"/>
     </row>
@@ -3259,7 +3490,7 @@
         <v>114</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="Q27"/>
     </row>
@@ -3283,192 +3514,201 @@
     </row>
     <row r="30" spans="1:17">
       <c r="A30" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C30" s="1">
-        <v>700</v>
-      </c>
-      <c r="D30" s="1">
-        <v>700</v>
+        <v>92</v>
       </c>
       <c r="E30" s="1">
-        <v>700</v>
-      </c>
-      <c r="F30" s="1">
-        <v>700</v>
-      </c>
-      <c r="G30" s="1">
-        <v>700</v>
-      </c>
-      <c r="H30" s="1">
-        <v>700</v>
+        <v>980</v>
       </c>
       <c r="Q30"/>
     </row>
     <row r="31" spans="1:17">
       <c r="A31" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C31" s="1">
-        <v>50</v>
+        <v>700</v>
       </c>
       <c r="D31" s="1">
-        <v>50</v>
+        <v>700</v>
       </c>
       <c r="E31" s="1">
-        <v>50</v>
+        <v>700</v>
       </c>
       <c r="F31" s="1">
-        <v>50</v>
+        <v>700</v>
       </c>
       <c r="G31" s="1">
-        <v>50</v>
+        <v>700</v>
       </c>
       <c r="H31" s="1">
-        <v>50</v>
+        <v>700</v>
       </c>
       <c r="Q31"/>
     </row>
     <row r="32" spans="1:17">
       <c r="A32" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C32" s="1">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D32" s="1">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E32" s="1">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F32" s="1">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G32" s="1">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="H32" s="1">
-        <v>52</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="Q32"/>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C33" s="5">
-        <f>C35</f>
-        <v>150</v>
-      </c>
-      <c r="D33" s="5">
-        <f>C34</f>
-        <v>164.5</v>
-      </c>
-      <c r="E33" s="5">
-        <f t="shared" ref="E33:H33" si="8">D34</f>
-        <v>171.5</v>
-      </c>
-      <c r="F33" s="5">
-        <f t="shared" si="8"/>
-        <v>178.5</v>
-      </c>
-      <c r="G33" s="5">
-        <f t="shared" si="8"/>
-        <v>185.5</v>
-      </c>
-      <c r="H33" s="5">
-        <f t="shared" si="8"/>
-        <v>191.5</v>
+        <v>25</v>
+      </c>
+      <c r="C33" s="1">
+        <v>52</v>
+      </c>
+      <c r="D33" s="1">
+        <v>52</v>
+      </c>
+      <c r="E33" s="1">
+        <v>52</v>
+      </c>
+      <c r="F33" s="1">
+        <v>52</v>
+      </c>
+      <c r="G33" s="1">
+        <v>52</v>
+      </c>
+      <c r="H33" s="1">
+        <v>52</v>
       </c>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C34" s="5">
-        <f>AVERAGE(C36,D35)</f>
+        <f>C36</f>
+        <v>150</v>
+      </c>
+      <c r="D34" s="5">
+        <f>C35</f>
         <v>164.5</v>
       </c>
-      <c r="D34" s="5">
-        <f>AVERAGE(D36,E35)</f>
+      <c r="E34" s="5">
+        <f t="shared" ref="E34:H34" si="8">D35</f>
         <v>171.5</v>
       </c>
-      <c r="E34" s="5">
-        <f>AVERAGE(E36,F35)</f>
+      <c r="F34" s="5">
+        <f t="shared" si="8"/>
         <v>178.5</v>
       </c>
-      <c r="F34" s="5">
-        <f>AVERAGE(F36,G35)</f>
+      <c r="G34" s="5">
+        <f>F35</f>
         <v>185.5</v>
       </c>
-      <c r="G34" s="5">
-        <f>AVERAGE(G36,H35)</f>
+      <c r="H34" s="5">
+        <f t="shared" si="8"/>
         <v>191.5</v>
-      </c>
-      <c r="H34" s="5">
-        <f>H36</f>
-        <v>200</v>
       </c>
     </row>
     <row r="35" spans="1:9">
-      <c r="C35" s="1">
-        <v>150</v>
-      </c>
-      <c r="D35" s="1">
-        <v>165</v>
-      </c>
-      <c r="E35" s="1">
-        <v>172</v>
-      </c>
-      <c r="F35" s="1">
-        <v>179</v>
-      </c>
-      <c r="G35" s="1">
-        <v>186</v>
-      </c>
-      <c r="H35" s="1">
-        <v>192</v>
-      </c>
-      <c r="I35" s="1" t="s">
-        <v>60</v>
+      <c r="A35" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C35" s="5">
+        <f>AVERAGE(C37,D36)</f>
+        <v>164.5</v>
+      </c>
+      <c r="D35" s="5">
+        <f>AVERAGE(D37,E36)</f>
+        <v>171.5</v>
+      </c>
+      <c r="E35" s="5">
+        <f>AVERAGE(E37,F36)</f>
+        <v>178.5</v>
+      </c>
+      <c r="F35" s="5">
+        <f>AVERAGE(F37,G36)</f>
+        <v>185.5</v>
+      </c>
+      <c r="G35" s="5">
+        <f>AVERAGE(G37,H36)</f>
+        <v>191.5</v>
+      </c>
+      <c r="H35" s="5">
+        <f>H37</f>
+        <v>200</v>
       </c>
     </row>
     <row r="36" spans="1:9">
       <c r="C36" s="1">
+        <v>150</v>
+      </c>
+      <c r="D36" s="1">
+        <v>165</v>
+      </c>
+      <c r="E36" s="1">
+        <v>172</v>
+      </c>
+      <c r="F36" s="1">
+        <v>179</v>
+      </c>
+      <c r="G36" s="1">
+        <v>186</v>
+      </c>
+      <c r="H36" s="1">
+        <v>192</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="C37" s="1">
         <v>164</v>
       </c>
-      <c r="D36" s="1">
-        <f>E35-1</f>
+      <c r="D37" s="1">
+        <f>E36-1</f>
         <v>171</v>
       </c>
-      <c r="E36" s="1">
-        <f t="shared" ref="E36:G36" si="9">F35-1</f>
+      <c r="E37" s="1">
+        <f t="shared" ref="E37:G37" si="9">F36-1</f>
         <v>178</v>
       </c>
-      <c r="F36" s="1">
-        <f t="shared" si="9"/>
+      <c r="F37" s="1">
+        <f>G36-1</f>
         <v>185</v>
       </c>
-      <c r="G36" s="1">
+      <c r="G37" s="1">
         <f t="shared" si="9"/>
         <v>191</v>
       </c>
-      <c r="H36" s="1">
+      <c r="H37" s="1">
         <v>200</v>
       </c>
     </row>

--- a/data/gravel/Wilier Rave SLR ID2 2025.xlsx
+++ b/data/gravel/Wilier Rave SLR ID2 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel copy/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1E8B0A5-2EE9-734F-BA26-93C88B81D5DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74E57ACF-3591-1543-B7DD-76A96A6147BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="13120" windowHeight="6100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="21380" windowHeight="13720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="105">
   <si>
     <t>brand</t>
   </si>
@@ -244,9 +244,6 @@
     <t>bottom_bracket</t>
   </si>
   <si>
-    <t>pf</t>
-  </si>
-  <si>
     <t>q_factor</t>
   </si>
   <si>
@@ -335,17 +332,26 @@
   </si>
   <si>
     <t>rigid</t>
+  </si>
+  <si>
+    <t>press fit</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="Futura"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Futura"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -368,8 +374,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1280,26 +1287,26 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
+        <v>98</v>
+      </c>
+      <c r="B36" t="s">
         <v>99</v>
-      </c>
-      <c r="B36" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
+        <v>100</v>
+      </c>
+      <c r="B37" t="s">
         <v>101</v>
-      </c>
-      <c r="B37" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>102</v>
+      </c>
+      <c r="B38" t="s">
         <v>103</v>
-      </c>
-      <c r="B38" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
@@ -1343,33 +1350,21 @@
       <c r="A44" t="s">
         <v>66</v>
       </c>
-      <c r="B44" t="s">
-        <v>67</v>
-      </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>68</v>
       </c>
-      <c r="B45" t="s">
-        <v>67</v>
-      </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>69</v>
       </c>
-      <c r="B46" t="s">
-        <v>67</v>
-      </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>70</v>
       </c>
-      <c r="B47" t="s">
-        <v>67</v>
-      </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
@@ -1385,23 +1380,23 @@
       <c r="A50" t="s">
         <v>73</v>
       </c>
-      <c r="B50" t="s">
-        <v>74</v>
+      <c r="B50" s="1" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B53" t="s">
         <v>67</v>
@@ -1409,50 +1404,50 @@
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
+        <v>77</v>
+      </c>
+      <c r="B54" t="s">
         <v>78</v>
-      </c>
-      <c r="B54" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B62" t="s">
         <v>67</v>
@@ -1460,57 +1455,57 @@
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Wilier Rave SLR ID2 2025.xlsx
+++ b/data/gravel/Wilier Rave SLR ID2 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74E57ACF-3591-1543-B7DD-76A96A6147BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1EF9D16-BC6D-624C-A617-D904ED06C7E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="21380" windowHeight="13720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="106">
   <si>
     <t>brand</t>
   </si>
@@ -335,6 +335,9 @@
   </si>
   <si>
     <t>press fit</t>
+  </si>
+  <si>
+    <t>https://wilier-cdn.thron.com/delivery/public/image/wilier/12a4e770-e208-49d2-a675-7b07d4bab8ac/gvltaa/std/5040x3078/_c9_1?scalemode=product&amp;format=webp</t>
   </si>
 </sst>
 </file>
@@ -719,6 +722,11 @@
         <v>8</v>
       </c>
     </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>105</v>
+      </c>
+    </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>10</v>

--- a/data/gravel/Wilier Rave SLR ID2 2025.xlsx
+++ b/data/gravel/Wilier Rave SLR ID2 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1EF9D16-BC6D-624C-A617-D904ED06C7E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{582A32D3-3B09-024E-8382-0C44FEF8D290}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="21380" windowHeight="13720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7420" yWindow="500" windowWidth="21380" windowHeight="13720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="107">
   <si>
     <t>brand</t>
   </si>
@@ -208,9 +208,6 @@
     <t>dropout</t>
   </si>
   <si>
-    <t>0</t>
-  </si>
-  <si>
     <t>tire_width_max_700c</t>
   </si>
   <si>
@@ -338,6 +335,12 @@
   </si>
   <si>
     <t>https://wilier-cdn.thron.com/delivery/public/image/wilier/12a4e770-e208-49d2-a675-7b07d4bab8ac/gvltaa/std/5040x3078/_c9_1?scalemode=product&amp;format=webp</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Rossano Veneto, Italy</t>
   </si>
 </sst>
 </file>
@@ -676,7 +679,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H73"/>
+  <dimension ref="A1:H74"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -724,7 +727,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
@@ -1295,26 +1298,26 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
+        <v>97</v>
+      </c>
+      <c r="B36" t="s">
         <v>98</v>
-      </c>
-      <c r="B36" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
+        <v>99</v>
+      </c>
+      <c r="B37" t="s">
         <v>100</v>
-      </c>
-      <c r="B37" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>101</v>
+      </c>
+      <c r="B38" t="s">
         <v>102</v>
-      </c>
-      <c r="B38" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
@@ -1337,183 +1340,188 @@
       <c r="A41" t="s">
         <v>61</v>
       </c>
-      <c r="B41" t="s">
-        <v>62</v>
-      </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
+        <v>62</v>
+      </c>
+      <c r="B42" t="s">
         <v>63</v>
-      </c>
-      <c r="B42" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B53" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
+        <v>76</v>
+      </c>
+      <c r="B54" t="s">
         <v>77</v>
-      </c>
-      <c r="B54" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B62" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A66" t="s">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A67" t="s">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A68" t="s">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A69" t="s">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A70" t="s">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A72" t="s">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
-        <v>97</v>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>105</v>
+      </c>
+      <c r="B74" t="s">
+        <v>106</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Wilier Rave SLR ID2 2025.xlsx
+++ b/data/gravel/Wilier Rave SLR ID2 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{582A32D3-3B09-024E-8382-0C44FEF8D290}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{466BF1D8-92B3-F547-BF57-89CD0CF04A88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7420" yWindow="500" windowWidth="21380" windowHeight="13720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="108">
   <si>
     <t>brand</t>
   </si>
@@ -341,6 +341,9 @@
   </si>
   <si>
     <t>Rossano Veneto, Italy</t>
+  </si>
+  <si>
+    <t>EUR</t>
   </si>
 </sst>
 </file>
@@ -1500,11 +1503,17 @@
       <c r="A70" t="s">
         <v>93</v>
       </c>
+      <c r="B70">
+        <v>4200</v>
+      </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>94</v>
       </c>
+      <c r="B71">
+        <v>4400</v>
+      </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
@@ -1514,6 +1523,9 @@
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>96</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">

--- a/data/gravel/Wilier Rave SLR ID2 2025.xlsx
+++ b/data/gravel/Wilier Rave SLR ID2 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{466BF1D8-92B3-F547-BF57-89CD0CF04A88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AED9DD85-8439-5A45-B4C9-AD96E5F30E9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7420" yWindow="500" windowWidth="21380" windowHeight="13720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="114">
   <si>
     <t>brand</t>
   </si>
@@ -344,6 +344,24 @@
   </si>
   <si>
     <t>EUR</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -682,7 +700,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H74"/>
+  <dimension ref="A1:H80"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1389,150 +1407,180 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>72</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>73</v>
+        <v>109</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>74</v>
+        <v>110</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>75</v>
-      </c>
-      <c r="B53" t="s">
-        <v>66</v>
+        <v>111</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>76</v>
-      </c>
-      <c r="B54" t="s">
-        <v>77</v>
+        <v>112</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>79</v>
+        <v>72</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>82</v>
+        <v>75</v>
+      </c>
+      <c r="B59" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>83</v>
+        <v>76</v>
+      </c>
+      <c r="B60" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>85</v>
-      </c>
-      <c r="B62" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>91</v>
+        <v>85</v>
+      </c>
+      <c r="B68" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>93</v>
-      </c>
-      <c r="B70">
-        <v>4200</v>
+        <v>87</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>94</v>
-      </c>
-      <c r="B71">
-        <v>4400</v>
+        <v>88</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>96</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>107</v>
+        <v>90</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>93</v>
+      </c>
+      <c r="B76">
+        <v>4200</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>94</v>
+      </c>
+      <c r="B77">
+        <v>4400</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>96</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
         <v>105</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B80" t="s">
         <v>106</v>
       </c>
     </row>
